--- a/business_forms/050_equipment_lifecycle_optimization_application_form--business_forms.xlsx
+++ b/business_forms/050_equipment_lifecycle_optimization_application_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'type_a'}</t>
+          <t>type_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Type A'}</t>
+          <t>Type A</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'type_b'}</t>
+          <t>type_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Type B'}</t>
+          <t>Type B</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'type_c'}</t>
+          <t>type_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Type C'}</t>
+          <t>Type C</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'decommissioned'}</t>
+          <t>decommissioned</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Decommissioned'}</t>
+          <t>Decommissioned</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'location_a'}</t>
+          <t>location_a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Location A'}</t>
+          <t>Location A</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'location_b'}</t>
+          <t>location_b</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Location B'}</t>
+          <t>Location B</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'location_c'}</t>
+          <t>location_c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Location C'}</t>
+          <t>Location C</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'user_3'}</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'User 3'}</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_review'}</t>
+          <t>in_review</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In Review'}</t>
+          <t>In Review</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending_review'}</t>
+          <t>pending_review</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Pending Review'}</t>
+          <t>Pending Review</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category_a'}</t>
+          <t>category_a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Category A'}</t>
+          <t>Category A</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category_b'}</t>
+          <t>category_b</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Category B'}</t>
+          <t>Category B</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'category_c'}</t>
+          <t>category_c</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Category C'}</t>
+          <t>Category C</t>
         </is>
       </c>
     </row>
